--- a/diss/zap_mes.xlsx
+++ b/diss/zap_mes.xlsx
@@ -2,18 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
-  <workbookPr/>
+  <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PVT_TSU\diss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACAB1B5F-DF84-4F68-AA01-29E43CE468F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD66A50-737B-4C13-8DFC-04FE9CF30EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3705" yWindow="735" windowWidth="15375" windowHeight="7875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="to_model" sheetId="1" r:id="rId1"/>
+    <sheet name="init_composition" sheetId="2" r:id="rId1"/>
+    <sheet name="to_model" sheetId="1" r:id="rId2"/>
+    <sheet name="SEPTEST" sheetId="3" r:id="rId3"/>
+    <sheet name="CCE" sheetId="5" r:id="rId4"/>
+    <sheet name="DL" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
   <si>
     <t>N2</t>
   </si>
@@ -160,6 +164,108 @@
   </si>
   <si>
     <t>C3</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>He</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>C2H6</t>
+  </si>
+  <si>
+    <t>C3H8</t>
+  </si>
+  <si>
+    <t>i-C4H10</t>
+  </si>
+  <si>
+    <t>n-C4H10</t>
+  </si>
+  <si>
+    <t>i-C5H12</t>
+  </si>
+  <si>
+    <t>n-C5H12</t>
+  </si>
+  <si>
+    <t>C36+</t>
+  </si>
+  <si>
+    <t>Pres</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Pb</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>Pst</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Vг ст</t>
+  </si>
+  <si>
+    <t>Vг тот</t>
+  </si>
+  <si>
+    <t>Vн</t>
+  </si>
+  <si>
+    <t>GOR</t>
+  </si>
+  <si>
+    <t>Bo</t>
+  </si>
+  <si>
+    <t>oden</t>
+  </si>
+  <si>
+    <t>Rs</t>
+  </si>
+  <si>
+    <t>PstTst</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>gden</t>
+  </si>
+  <si>
+    <t>Bg</t>
+  </si>
+  <si>
+    <t>mug</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>v/vres</t>
+  </si>
+  <si>
+    <t>v/vsat</t>
+  </si>
+  <si>
+    <t>compres</t>
   </si>
 </sst>
 </file>
@@ -195,8 +301,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -476,7 +583,486 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB5C0D2-7F79-482B-BC4D-B0E55C50AA90}">
+  <sheetPr codeName="Лист1"/>
+  <dimension ref="A1:D42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3">
+        <v>28.01</v>
+      </c>
+      <c r="C3">
+        <v>3.3399999999999999E-2</v>
+      </c>
+      <c r="D3">
+        <f>C3+C1+C2</f>
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>44.01</v>
+      </c>
+      <c r="C4">
+        <v>2.0899999999999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5">
+        <v>16.04</v>
+      </c>
+      <c r="C5">
+        <v>25.933199999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6">
+        <v>30.07</v>
+      </c>
+      <c r="C6">
+        <v>5.3499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7">
+        <v>44.1</v>
+      </c>
+      <c r="C7">
+        <v>6.6E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8">
+        <v>58.12</v>
+      </c>
+      <c r="C8">
+        <v>5.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9">
+        <v>58.12</v>
+      </c>
+      <c r="C9">
+        <v>1.83E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10">
+        <v>72.150000000000006</v>
+      </c>
+      <c r="C10">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <v>72.150000000000006</v>
+      </c>
+      <c r="C11">
+        <v>4.5999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>84</v>
+      </c>
+      <c r="C12">
+        <v>2.58E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>96</v>
+      </c>
+      <c r="C13">
+        <v>1.3299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>107</v>
+      </c>
+      <c r="C14">
+        <v>2.5899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>121</v>
+      </c>
+      <c r="C15">
+        <v>2.93E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>134</v>
+      </c>
+      <c r="C16">
+        <v>0.27279999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>147</v>
+      </c>
+      <c r="C17">
+        <v>0.97870000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>161</v>
+      </c>
+      <c r="C18">
+        <v>1.9490000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>175</v>
+      </c>
+      <c r="C19">
+        <v>3.6414</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>190</v>
+      </c>
+      <c r="C20">
+        <v>5.3917000000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>206</v>
+      </c>
+      <c r="C21">
+        <v>6.3574999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22">
+        <v>222</v>
+      </c>
+      <c r="C22">
+        <v>5.8072999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23">
+        <v>237</v>
+      </c>
+      <c r="C23">
+        <v>5.2316000000000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24">
+        <v>251</v>
+      </c>
+      <c r="C24">
+        <v>4.8459000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>263</v>
+      </c>
+      <c r="C25">
+        <v>4.4055999999999997</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26">
+        <v>275</v>
+      </c>
+      <c r="C26">
+        <v>3.8807999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>291</v>
+      </c>
+      <c r="C27">
+        <v>3.3334999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28">
+        <v>305</v>
+      </c>
+      <c r="C28">
+        <v>2.851</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29">
+        <v>318</v>
+      </c>
+      <c r="C29">
+        <v>2.4415</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30">
+        <v>331</v>
+      </c>
+      <c r="C30">
+        <v>2.1208999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31">
+        <v>345</v>
+      </c>
+      <c r="C31">
+        <v>1.8269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32">
+        <v>359</v>
+      </c>
+      <c r="C32">
+        <v>1.6054999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33">
+        <v>374</v>
+      </c>
+      <c r="C33">
+        <v>1.4240999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34">
+        <v>388</v>
+      </c>
+      <c r="C34">
+        <v>1.2457</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35">
+        <v>402</v>
+      </c>
+      <c r="C35">
+        <v>1.1254999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36">
+        <v>416</v>
+      </c>
+      <c r="C36">
+        <v>0.91300000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37">
+        <v>430</v>
+      </c>
+      <c r="C37">
+        <v>0.75970000000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38">
+        <v>444</v>
+      </c>
+      <c r="C38">
+        <v>0.64649999999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39">
+        <v>458</v>
+      </c>
+      <c r="C39">
+        <v>0.55349999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40">
+        <v>472</v>
+      </c>
+      <c r="C40">
+        <v>0.51559999999999995</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41">
+        <v>486</v>
+      </c>
+      <c r="C41">
+        <v>0.46889999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42">
+        <v>595.41</v>
+      </c>
+      <c r="C42">
+        <v>9.2317</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Лист2"/>
   <dimension ref="A1:B41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -496,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>5.0000000000000002E-5</v>
+        <v>3.4000000000000002E-4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -504,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>4.1E-5</v>
+        <v>2.0899999999999998E-4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -512,7 +1098,7 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>1.8277000000000002E-2</v>
+        <v>0.25933200000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -520,7 +1106,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>7.2999999999999999E-5</v>
+        <v>5.3499999999999999E-4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -528,7 +1114,7 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>4.0000000000000003E-5</v>
+        <v>6.6000000000000005E-5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -536,7 +1122,7 @@
         <v>34</v>
       </c>
       <c r="B7">
-        <v>3.7000000000000005E-5</v>
+        <v>5.1000000000000006E-5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -544,7 +1130,7 @@
         <v>35</v>
       </c>
       <c r="B8">
-        <v>8.6000000000000003E-5</v>
+        <v>1.83E-4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -552,7 +1138,7 @@
         <v>36</v>
       </c>
       <c r="B9">
-        <v>1.12E-4</v>
+        <v>4.0000000000000003E-5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -560,7 +1146,7 @@
         <v>37</v>
       </c>
       <c r="B10">
-        <v>9.1000000000000003E-5</v>
+        <v>4.6E-5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -568,7 +1154,7 @@
         <v>2</v>
       </c>
       <c r="B11">
-        <v>1.8700000000000002E-4</v>
+        <v>2.5799999999999998E-4</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -576,7 +1162,7 @@
         <v>3</v>
       </c>
       <c r="B12">
-        <v>1.9099999999999998E-4</v>
+        <v>1.3299999999999998E-4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -584,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="B13">
-        <v>1.2400000000000001E-4</v>
+        <v>2.5900000000000001E-4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -592,7 +1178,7 @@
         <v>5</v>
       </c>
       <c r="B14">
-        <v>1.46E-4</v>
+        <v>2.9300000000000002E-4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -600,7 +1186,7 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>1.5989999999999999E-3</v>
+        <v>2.728E-3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -608,7 +1194,7 @@
         <v>7</v>
       </c>
       <c r="B16">
-        <v>8.202000000000001E-3</v>
+        <v>9.7870000000000006E-3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -616,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="B17">
-        <v>1.4860999999999999E-2</v>
+        <v>1.949E-2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -624,7 +1210,7 @@
         <v>9</v>
       </c>
       <c r="B18">
-        <v>3.024E-2</v>
+        <v>3.6414000000000002E-2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -632,7 +1218,7 @@
         <v>10</v>
       </c>
       <c r="B19">
-        <v>3.5359000000000002E-2</v>
+        <v>5.3917E-2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -640,7 +1226,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>3.7812999999999999E-2</v>
+        <v>6.3574999999999993E-2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -648,7 +1234,7 @@
         <v>12</v>
       </c>
       <c r="B21">
-        <v>3.9809999999999998E-2</v>
+        <v>5.8073E-2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -656,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="B22">
-        <v>4.1513999999999995E-2</v>
+        <v>5.2316000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -664,7 +1250,7 @@
         <v>14</v>
       </c>
       <c r="B23">
-        <v>4.2723000000000004E-2</v>
+        <v>4.8459000000000002E-2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -672,7 +1258,7 @@
         <v>15</v>
       </c>
       <c r="B24">
-        <v>4.2895000000000003E-2</v>
+        <v>4.4055999999999998E-2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -680,7 +1266,7 @@
         <v>16</v>
       </c>
       <c r="B25">
-        <v>4.1838E-2</v>
+        <v>3.8807999999999995E-2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -688,7 +1274,7 @@
         <v>17</v>
       </c>
       <c r="B26">
-        <v>3.8460000000000001E-2</v>
+        <v>3.3334999999999997E-2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -696,7 +1282,7 @@
         <v>18</v>
       </c>
       <c r="B27">
-        <v>3.5514000000000004E-2</v>
+        <v>2.8510000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -704,7 +1290,7 @@
         <v>19</v>
       </c>
       <c r="B28">
-        <v>3.3195000000000002E-2</v>
+        <v>2.4414999999999999E-2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -712,7 +1298,7 @@
         <v>20</v>
       </c>
       <c r="B29">
-        <v>3.1213000000000001E-2</v>
+        <v>2.1208999999999999E-2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -720,7 +1306,7 @@
         <v>21</v>
       </c>
       <c r="B30">
-        <v>3.0203000000000001E-2</v>
+        <v>1.8269000000000001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -728,7 +1314,7 @@
         <v>22</v>
       </c>
       <c r="B31">
-        <v>2.8388E-2</v>
+        <v>1.6055E-2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -736,7 +1322,7 @@
         <v>23</v>
       </c>
       <c r="B32">
-        <v>2.6259000000000001E-2</v>
+        <v>1.4240999999999998E-2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -744,7 +1330,7 @@
         <v>24</v>
       </c>
       <c r="B33">
-        <v>2.5476000000000002E-2</v>
+        <v>1.2457000000000001E-2</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -752,7 +1338,7 @@
         <v>25</v>
       </c>
       <c r="B34">
-        <v>2.3765000000000001E-2</v>
+        <v>1.1254999999999999E-2</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -760,7 +1346,7 @@
         <v>26</v>
       </c>
       <c r="B35">
-        <v>2.0541E-2</v>
+        <v>9.130000000000001E-3</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -768,7 +1354,7 @@
         <v>27</v>
       </c>
       <c r="B36">
-        <v>1.8585000000000001E-2</v>
+        <v>7.5970000000000005E-3</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -776,7 +1362,7 @@
         <v>28</v>
       </c>
       <c r="B37">
-        <v>1.7131E-2</v>
+        <v>6.4649999999999994E-3</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -784,7 +1370,7 @@
         <v>29</v>
       </c>
       <c r="B38">
-        <v>1.4103000000000001E-2</v>
+        <v>5.535E-3</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -792,7 +1378,7 @@
         <v>30</v>
       </c>
       <c r="B39">
-        <v>1.2095E-2</v>
+        <v>5.1559999999999991E-3</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -800,7 +1386,7 @@
         <v>31</v>
       </c>
       <c r="B40">
-        <v>1.0331999999999999E-2</v>
+        <v>4.6889999999999996E-3</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -808,10 +1394,670 @@
         <v>38</v>
       </c>
       <c r="B41">
-        <v>0.27843200000000001</v>
+        <v>9.2316999999999996E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51D33C0-F789-4F7C-8C28-7009348FCFFA}">
+  <sheetPr codeName="Лист3"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2">
+        <v>88.179000000000002</v>
+      </c>
+      <c r="G2">
+        <v>26.37</v>
+      </c>
+      <c r="H2">
+        <v>1.0580000000000001</v>
+      </c>
+      <c r="I2">
+        <v>918.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3">
+        <v>7.38</v>
+      </c>
+      <c r="C3">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3">
+        <v>88.231999999999999</v>
+      </c>
+      <c r="G3">
+        <v>26.37</v>
+      </c>
+      <c r="H3">
+        <v>1.0589999999999999</v>
+      </c>
+      <c r="I3">
+        <v>918.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4">
+        <v>0.8</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>1973</v>
+      </c>
+      <c r="E4">
+        <v>1973</v>
+      </c>
+      <c r="F4">
+        <v>83.677999999999997</v>
+      </c>
+      <c r="G4">
+        <v>23.67</v>
+      </c>
+      <c r="H4">
+        <v>1.004</v>
+      </c>
+      <c r="I4">
+        <v>952.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5">
+        <v>0.3</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5">
+        <v>142</v>
+      </c>
+      <c r="E5">
+        <v>2114</v>
+      </c>
+      <c r="F5">
+        <v>83.512</v>
+      </c>
+      <c r="G5">
+        <v>1.7</v>
+      </c>
+      <c r="H5">
+        <v>1.002</v>
+      </c>
+      <c r="I5">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6">
+        <v>0.1</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>83</v>
+      </c>
+      <c r="E6">
+        <v>2198</v>
+      </c>
+      <c r="F6">
+        <v>83.344999999999999</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>954.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <f>G3-G4</f>
+        <v>2.6999999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10AD0EDF-56D4-41E6-8AEE-54CAF03946A0}">
+  <sheetPr codeName="Лист4"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="B2">
+        <v>152.697</v>
+      </c>
+      <c r="C2">
+        <v>0.99099999999999999</v>
+      </c>
+      <c r="D2">
+        <v>0.98899999999999999</v>
+      </c>
+      <c r="E2">
+        <v>927.6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2">
+        <f>E2/1000</f>
+        <v>0.92759999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>16.96</v>
+      </c>
+      <c r="B3">
+        <v>152.86199999999999</v>
+      </c>
+      <c r="C3">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="D3">
+        <v>0.99</v>
+      </c>
+      <c r="E3">
+        <v>926.6</v>
+      </c>
+      <c r="F3" s="1">
+        <v>8.9899999999999995E-4</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G8" si="0">E3/1000</f>
+        <v>0.92659999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>15.18</v>
+      </c>
+      <c r="B4">
+        <v>153.113</v>
+      </c>
+      <c r="C4">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="D4">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="E4">
+        <v>925.1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>9.1500000000000001E-4</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>0.92510000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>13.54</v>
+      </c>
+      <c r="B5">
+        <v>153.34800000000001</v>
+      </c>
+      <c r="C5">
+        <v>0.995</v>
+      </c>
+      <c r="D5">
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="E5">
+        <v>923.7</v>
+      </c>
+      <c r="F5" s="1">
+        <v>9.2800000000000001E-4</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>0.92370000000000008</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>11.1</v>
+      </c>
+      <c r="B6">
+        <v>153.70099999999999</v>
+      </c>
+      <c r="C6">
+        <v>0.997</v>
+      </c>
+      <c r="D6">
+        <v>0.996</v>
+      </c>
+      <c r="E6">
+        <v>921.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>9.3999999999999997E-4</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0.92149999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>9.65</v>
+      </c>
+      <c r="B7">
+        <v>153.91399999999999</v>
+      </c>
+      <c r="C7">
+        <v>0.998</v>
+      </c>
+      <c r="D7">
+        <v>0.997</v>
+      </c>
+      <c r="E7">
+        <v>920.3</v>
+      </c>
+      <c r="F7" s="1">
+        <v>9.5100000000000002E-4</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.92030000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>154.15899999999999</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0.999</v>
+      </c>
+      <c r="E8">
+        <v>918.8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>9.6400000000000001E-4</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>0.91879999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A3E5CA-6F3A-420B-A91E-6F5C8D3A9F0D}">
+  <sheetPr codeName="Лист5"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>27.61</v>
+      </c>
+      <c r="D2">
+        <v>1.06</v>
+      </c>
+      <c r="E2">
+        <v>918.5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>7.38</v>
+      </c>
+      <c r="C3">
+        <v>27.61</v>
+      </c>
+      <c r="D3">
+        <v>1.0609999999999999</v>
+      </c>
+      <c r="E3">
+        <v>917.2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>6.3</v>
+      </c>
+      <c r="C4">
+        <v>24.02</v>
+      </c>
+      <c r="D4">
+        <v>1.052</v>
+      </c>
+      <c r="E4">
+        <v>922.8</v>
+      </c>
+      <c r="F4">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="G4">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="H4">
+        <v>1.41E-2</v>
+      </c>
+      <c r="I4">
+        <v>9.4000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C5">
+        <v>19.760000000000002</v>
+      </c>
+      <c r="D5">
+        <v>1.042</v>
+      </c>
+      <c r="E5">
+        <v>929.2</v>
+      </c>
+      <c r="F5">
+        <v>0.91539999999999999</v>
+      </c>
+      <c r="G5">
+        <v>3.7699999999999997E-2</v>
+      </c>
+      <c r="H5">
+        <v>1.78E-2</v>
+      </c>
+      <c r="I5">
+        <v>8.6999999999999994E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>3.9</v>
+      </c>
+      <c r="C6">
+        <v>15.11</v>
+      </c>
+      <c r="D6">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="E6">
+        <v>935.5</v>
+      </c>
+      <c r="F6">
+        <v>0.93859999999999999</v>
+      </c>
+      <c r="G6">
+        <v>2.81E-2</v>
+      </c>
+      <c r="H6">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="I6">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>2.7</v>
+      </c>
+      <c r="C7">
+        <v>10.16</v>
+      </c>
+      <c r="D7">
+        <v>1.0209999999999999</v>
+      </c>
+      <c r="E7">
+        <v>941.9</v>
+      </c>
+      <c r="F7">
+        <v>0.96230000000000004</v>
+      </c>
+      <c r="G7">
+        <v>1.9E-2</v>
+      </c>
+      <c r="H7">
+        <v>3.5400000000000001E-2</v>
+      </c>
+      <c r="I7">
+        <v>7.4000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8">
+        <v>5.29</v>
+      </c>
+      <c r="D8">
+        <v>1.01</v>
+      </c>
+      <c r="E8">
+        <v>948.3</v>
+      </c>
+      <c r="F8">
+        <v>0.98560000000000003</v>
+      </c>
+      <c r="G8">
+        <v>1.03E-2</v>
+      </c>
+      <c r="H8">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="I8">
+        <v>6.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9">
+        <v>0.1</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0.999</v>
+      </c>
+      <c r="E9">
+        <v>955.7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="H9">
+        <v>0.99439999999999995</v>
+      </c>
+      <c r="I9">
+        <v>6.3E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10">
+        <v>0.1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>954.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>